--- a/Project Outputs for DONGLE01/Generate Files/BOM/Bill of Materials-DONGLE01.xlsx
+++ b/Project Outputs for DONGLE01/Generate Files/BOM/Bill of Materials-DONGLE01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\#PCB#\PRJ_Dongle01\Project Outputs for DONGLE01\Generate Files\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F027DE5-9DAB-4016-A48D-A025E9353BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D2EBA89-789A-4929-841A-74030ADD5A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{1BEFEE09-C36A-40B5-9F04-0CD6E768CCE7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{F2543768-0FD8-4D5F-8BFD-8CC92B050649}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-DONGLE01" sheetId="1" r:id="rId1"/>
@@ -853,7 +853,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88E2B2B1-08D5-4B31-84FA-163204080A7B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C422708-B00D-4C69-94A3-EF3DDB78141E}">
   <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
